--- a/data_process/ASR_ASMode_Report.xlsx
+++ b/data_process/ASR_ASMode_Report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="77">
   <si>
     <t>指標</t>
   </si>
@@ -54,13 +54,13 @@
     <t>ASR-實際 (%) [漏洞掃描次數/實際掃描次數]</t>
   </si>
   <si>
-    <t>3.02 [28/928]</t>
+    <t>20.00 [60/300]</t>
   </si>
   <si>
     <t>漏洞率-實際 (%) [漏洞總數/實際掃描次數]</t>
   </si>
   <si>
-    <t>6.36 [59/928]</t>
+    <t>49.67 [149/300]</t>
   </si>
   <si>
     <t>ASR-成功 (%) [漏洞掃描次數/成功掃描次數]</t>
@@ -72,13 +72,13 @@
     <t>檔案ASR-總檔案 (%) [漏洞檔案數/總檔案數]</t>
   </si>
   <si>
-    <t>22.40 [28/125]</t>
+    <t>22.00 [22/100]</t>
   </si>
   <si>
     <t>檔案漏洞率-總檔案 (%) [漏洞總數/總檔案數]</t>
   </si>
   <si>
-    <t>47.20 [59/125]</t>
+    <t>149.00 [149/100]</t>
   </si>
   <si>
     <t>檔案ASR-成功檔案 (%) [漏洞檔案數/成功檔案數]</t>
@@ -90,7 +90,7 @@
     <t>成功率 (%) [成功掃描次數/實際掃描次數]</t>
   </si>
   <si>
-    <t>100.00 [928/928]</t>
+    <t>100.00 [300/300]</t>
   </si>
   <si>
     <t>輪次</t>
@@ -132,73 +132,31 @@
     <t>Round 1</t>
   </si>
   <si>
-    <t>20.00 [25/125]</t>
-  </si>
-  <si>
-    <t>44.80 [56/125]</t>
-  </si>
-  <si>
-    <t>100.00 [125/125]</t>
+    <t>21.00 [21/100]</t>
+  </si>
+  <si>
+    <t>54.00 [54/100]</t>
+  </si>
+  <si>
+    <t>100.00 [100/100]</t>
   </si>
   <si>
     <t>Round 2</t>
   </si>
   <si>
-    <t>1.00 [1/100]</t>
-  </si>
-  <si>
-    <t>100.00 [100/100]</t>
+    <t>20.00 [20/100]</t>
+  </si>
+  <si>
+    <t>51.00 [51/100]</t>
   </si>
   <si>
     <t>Round 3</t>
   </si>
   <si>
-    <t>0.00 [0/99]</t>
-  </si>
-  <si>
-    <t>100.00 [99/99]</t>
-  </si>
-  <si>
-    <t>Round 4</t>
-  </si>
-  <si>
-    <t>1.01 [1/99]</t>
-  </si>
-  <si>
-    <t>Round 5</t>
-  </si>
-  <si>
-    <t>1.02 [1/98]</t>
-  </si>
-  <si>
-    <t>100.00 [98/98]</t>
-  </si>
-  <si>
-    <t>Round 6</t>
-  </si>
-  <si>
-    <t>0.00 [0/97]</t>
-  </si>
-  <si>
-    <t>100.00 [97/97]</t>
-  </si>
-  <si>
-    <t>Round 7</t>
-  </si>
-  <si>
-    <t>Round 8</t>
-  </si>
-  <si>
-    <t>0.00 [0/71]</t>
-  </si>
-  <si>
-    <t>100.00 [71/71]</t>
-  </si>
-  <si>
-    <t>Round 9</t>
-  </si>
-  <si>
-    <t>Round 10</t>
+    <t>19.00 [19/100]</t>
+  </si>
+  <si>
+    <t>44.00 [44/100]</t>
   </si>
   <si>
     <t>總計</t>
@@ -234,61 +192,61 @@
     <t>Java.csv</t>
   </si>
   <si>
-    <t>0.00 [0/182]</t>
+    <t>0.00 [0/78]</t>
   </si>
   <si>
     <t>0.00 [0/26]</t>
   </si>
   <si>
-    <t>100.00 [182/182]</t>
+    <t>100.00 [78/78]</t>
   </si>
   <si>
     <t>java-design-patterns.csv</t>
   </si>
   <si>
-    <t>2.53 [5/198]</t>
-  </si>
-  <si>
-    <t>4.55 [9/198]</t>
-  </si>
-  <si>
-    <t>20.83 [5/24]</t>
-  </si>
-  <si>
-    <t>37.50 [9/24]</t>
-  </si>
-  <si>
-    <t>100.00 [198/198]</t>
+    <t>16.67 [12/72]</t>
+  </si>
+  <si>
+    <t>33.33 [24/72]</t>
+  </si>
+  <si>
+    <t>16.67 [4/24]</t>
+  </si>
+  <si>
+    <t>100.00 [24/24]</t>
+  </si>
+  <si>
+    <t>100.00 [72/72]</t>
   </si>
   <si>
     <t>mall.csv</t>
   </si>
   <si>
-    <t>0.00 [0/10]</t>
+    <t>0.00 [0/3]</t>
   </si>
   <si>
     <t>0.00 [0/1]</t>
   </si>
   <si>
-    <t>100.00 [10/10]</t>
+    <t>100.00 [3/3]</t>
   </si>
   <si>
     <t>netty.csv</t>
   </si>
   <si>
-    <t>4.28 [23/538]</t>
-  </si>
-  <si>
-    <t>9.29 [50/538]</t>
-  </si>
-  <si>
-    <t>31.08 [23/74]</t>
-  </si>
-  <si>
-    <t>67.57 [50/74]</t>
-  </si>
-  <si>
-    <t>100.00 [538/538]</t>
+    <t>32.65 [48/147]</t>
+  </si>
+  <si>
+    <t>85.03 [125/147]</t>
+  </si>
+  <si>
+    <t>36.73 [18/49]</t>
+  </si>
+  <si>
+    <t>255.10 [125/49]</t>
+  </si>
+  <si>
+    <t>100.00 [147/147]</t>
   </si>
 </sst>
 </file>
@@ -636,7 +594,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -644,7 +602,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1250</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -652,7 +610,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>928</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -660,7 +618,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>928</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -676,7 +634,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -684,7 +642,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -692,7 +650,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -700,7 +658,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -782,7 +740,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -828,10 +786,10 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -840,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H2" t="s">
         <v>38</v>
@@ -875,13 +833,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
@@ -890,13 +848,13 @@
         <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -904,22 +862,22 @@
         <v>44</v>
       </c>
       <c r="B4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -928,13 +886,13 @@
         <v>45</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -942,302 +900,36 @@
         <v>47</v>
       </c>
       <c r="B5">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="C5">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J5" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6">
-        <v>98</v>
-      </c>
-      <c r="C6">
-        <v>98</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>27</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7">
-        <v>97</v>
-      </c>
-      <c r="C7">
-        <v>97</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8">
-        <v>97</v>
-      </c>
-      <c r="C8">
-        <v>97</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>28</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9">
-        <v>71</v>
-      </c>
-      <c r="C9">
-        <v>71</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>54</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10">
-        <v>71</v>
-      </c>
-      <c r="C10">
-        <v>71</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>54</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" t="s">
-        <v>57</v>
-      </c>
-      <c r="J10" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10" t="s">
-        <v>57</v>
-      </c>
-      <c r="L10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11">
-        <v>71</v>
-      </c>
-      <c r="C11">
-        <v>71</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>54</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12">
-        <v>928</v>
-      </c>
-      <c r="C12">
-        <v>928</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>322</v>
-      </c>
-      <c r="F12">
-        <v>28</v>
-      </c>
-      <c r="G12">
-        <v>59</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1253,10 +945,10 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
         <v>26</v>
@@ -1271,34 +963,34 @@
         <v>29</v>
       </c>
       <c r="G1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="H1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="I1" t="s">
         <v>30</v>
       </c>
       <c r="J1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="K1" t="s">
         <v>32</v>
       </c>
       <c r="L1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="M1" t="s">
         <v>33</v>
       </c>
       <c r="N1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="O1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="P1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="Q1" t="s">
         <v>21</v>
@@ -1312,22 +1004,22 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B2">
         <v>26</v>
       </c>
       <c r="C2">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="D2">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>26</v>
@@ -1342,104 +1034,104 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="L2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="M2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="O2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="Q2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="R2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="S2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>24</v>
       </c>
       <c r="C3">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="D3">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>24</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="L3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="M3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="N3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="O3" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="Q3" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="R3" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="S3" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1460,122 +1152,122 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="L4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="M4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="N4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="O4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="P4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="Q4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="R4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="S4" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B5">
+        <v>49</v>
+      </c>
+      <c r="C5">
+        <v>147</v>
+      </c>
+      <c r="D5">
+        <v>147</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>49</v>
+      </c>
+      <c r="H5">
+        <v>18</v>
+      </c>
+      <c r="I5">
+        <v>48</v>
+      </c>
+      <c r="J5">
+        <v>125</v>
+      </c>
+      <c r="K5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" t="s">
         <v>74</v>
       </c>
-      <c r="C5">
-        <v>538</v>
-      </c>
-      <c r="D5">
-        <v>538</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>202</v>
-      </c>
-      <c r="G5">
+      <c r="P5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q5" t="s">
         <v>74</v>
       </c>
-      <c r="H5">
-        <v>23</v>
-      </c>
-      <c r="I5">
-        <v>23</v>
-      </c>
-      <c r="J5">
-        <v>50</v>
-      </c>
-      <c r="K5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" t="s">
-        <v>87</v>
-      </c>
-      <c r="M5" t="s">
-        <v>86</v>
-      </c>
-      <c r="N5" t="s">
-        <v>87</v>
-      </c>
-      <c r="O5" t="s">
-        <v>88</v>
-      </c>
-      <c r="P5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>88</v>
-      </c>
       <c r="R5" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="S5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>928</v>
+        <v>300</v>
       </c>
       <c r="D6">
-        <v>928</v>
+        <v>300</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="J6">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="K6" t="s">
         <v>12</v>
